--- a/public/plantilla-inspeccion-maquinaria.xlsx
+++ b/public/plantilla-inspeccion-maquinaria.xlsx
@@ -15,6 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="hh:mm"/>
+  </numFmts>
   <fonts count="20">
     <font>
       <name val="Calibri"/>
@@ -554,19 +557,19 @@
     <xf numFmtId="4" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -615,7 +618,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -668,7 +671,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">

--- a/public/plantilla-inspeccion-maquinaria.xlsx
+++ b/public/plantilla-inspeccion-maquinaria.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="9" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inspección Maquinaria" sheetId="1" state="visible" r:id="rId1"/>

--- a/public/plantilla-inspeccion-maquinaria.xlsx
+++ b/public/plantilla-inspeccion-maquinaria.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inspección Maquinaria" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,9 +16,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="hh:mm"/>
+    <numFmt numFmtId="164" formatCode="hh:mm"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -163,6 +163,10 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -529,7 +533,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -560,7 +564,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -636,7 +640,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -757,6 +761,49 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1219,6 +1266,7 @@
   <cols>
     <col width="12.77734375" customWidth="1" style="27" min="1" max="1"/>
     <col width="13" customWidth="1" style="27" min="2" max="3"/>
+    <col width="13" customWidth="1" style="27" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="27" min="4" max="4"/>
     <col width="10" customWidth="1" style="27" min="5" max="5"/>
     <col width="15.77734375" customWidth="1" style="27" min="6" max="6"/>
@@ -1386,16 +1434,16 @@
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="25" t="n"/>
-      <c r="G11" s="25" t="n"/>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="25" t="n"/>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="25" t="n"/>
-      <c r="L11" s="22" t="n"/>
+      <c r="C11" s="97" t="n"/>
+      <c r="D11" s="98" t="n"/>
+      <c r="E11" s="98" t="n"/>
+      <c r="F11" s="98" t="n"/>
+      <c r="G11" s="98" t="n"/>
+      <c r="H11" s="98" t="n"/>
+      <c r="I11" s="98" t="n"/>
+      <c r="J11" s="98" t="n"/>
+      <c r="K11" s="98" t="n"/>
+      <c r="L11" s="99" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="27">
       <c r="A12" s="88" t="inlineStr">
@@ -1404,20 +1452,20 @@
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="22" t="n"/>
+      <c r="C12" s="97" t="n"/>
+      <c r="D12" s="98" t="n"/>
+      <c r="E12" s="98" t="n"/>
+      <c r="F12" s="98" t="n"/>
+      <c r="G12" s="99" t="n"/>
       <c r="H12" s="88" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I12" s="22" t="n"/>
-      <c r="J12" s="24" t="n"/>
-      <c r="K12" s="25" t="n"/>
-      <c r="L12" s="22" t="n"/>
+      <c r="J12" s="97" t="n"/>
+      <c r="K12" s="98" t="n"/>
+      <c r="L12" s="99" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="27">
       <c r="A13" s="88" t="inlineStr">
@@ -1426,24 +1474,24 @@
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="22" t="n"/>
+      <c r="C13" s="100" t="n"/>
+      <c r="D13" s="99" t="n"/>
       <c r="E13" s="88" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
       <c r="F13" s="22" t="n"/>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="22" t="n"/>
+      <c r="G13" s="101" t="n"/>
+      <c r="H13" s="99" t="n"/>
       <c r="I13" s="88" t="inlineStr">
         <is>
           <t>Inspección N°</t>
         </is>
       </c>
       <c r="J13" s="22" t="n"/>
-      <c r="K13" s="32" t="n"/>
-      <c r="L13" s="22" t="n"/>
+      <c r="K13" s="102" t="n"/>
+      <c r="L13" s="99" t="n"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="27">
       <c r="A14" s="77" t="inlineStr">
@@ -1470,20 +1518,20 @@
         </is>
       </c>
       <c r="B15" s="22" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="25" t="n"/>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="25" t="n"/>
-      <c r="G15" s="22" t="n"/>
+      <c r="C15" s="97" t="n"/>
+      <c r="D15" s="98" t="n"/>
+      <c r="E15" s="98" t="n"/>
+      <c r="F15" s="98" t="n"/>
+      <c r="G15" s="99" t="n"/>
       <c r="H15" s="88" t="inlineStr">
         <is>
           <t>Marca y modelo</t>
         </is>
       </c>
       <c r="I15" s="22" t="n"/>
-      <c r="J15" s="24" t="n"/>
-      <c r="K15" s="25" t="n"/>
-      <c r="L15" s="22" t="n"/>
+      <c r="J15" s="97" t="n"/>
+      <c r="K15" s="98" t="n"/>
+      <c r="L15" s="99" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1" s="27">
       <c r="A16" s="88" t="inlineStr">
@@ -1492,24 +1540,24 @@
         </is>
       </c>
       <c r="B16" s="22" t="n"/>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="22" t="n"/>
+      <c r="C16" s="102" t="n"/>
+      <c r="D16" s="99" t="n"/>
       <c r="E16" s="88" t="inlineStr">
         <is>
           <t>Propietario</t>
         </is>
       </c>
       <c r="F16" s="22" t="n"/>
-      <c r="G16" s="32" t="n"/>
-      <c r="H16" s="22" t="n"/>
+      <c r="G16" s="102" t="n"/>
+      <c r="H16" s="99" t="n"/>
       <c r="I16" s="88" t="inlineStr">
         <is>
           <t>Empresa propietaria</t>
         </is>
       </c>
       <c r="J16" s="22" t="n"/>
-      <c r="K16" s="24" t="n"/>
-      <c r="L16" s="22" t="n"/>
+      <c r="K16" s="97" t="n"/>
+      <c r="L16" s="99" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1" s="27">
       <c r="A17" s="88" t="inlineStr">
@@ -1518,20 +1566,20 @@
         </is>
       </c>
       <c r="B17" s="22" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="n"/>
-      <c r="G17" s="22" t="n"/>
+      <c r="C17" s="97" t="n"/>
+      <c r="D17" s="98" t="n"/>
+      <c r="E17" s="98" t="n"/>
+      <c r="F17" s="98" t="n"/>
+      <c r="G17" s="99" t="n"/>
       <c r="H17" s="88" t="inlineStr">
         <is>
           <t>Horómetro o kilometraje</t>
         </is>
       </c>
       <c r="I17" s="22" t="n"/>
-      <c r="J17" s="32" t="n"/>
-      <c r="K17" s="25" t="n"/>
-      <c r="L17" s="22" t="n"/>
+      <c r="J17" s="102" t="n"/>
+      <c r="K17" s="98" t="n"/>
+      <c r="L17" s="99" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1" s="27">
       <c r="A18" s="88" t="inlineStr">
@@ -1540,20 +1588,20 @@
         </is>
       </c>
       <c r="B18" s="22" t="n"/>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="25" t="n"/>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="25" t="n"/>
-      <c r="G18" s="22" t="n"/>
+      <c r="C18" s="97" t="n"/>
+      <c r="D18" s="98" t="n"/>
+      <c r="E18" s="98" t="n"/>
+      <c r="F18" s="98" t="n"/>
+      <c r="G18" s="99" t="n"/>
       <c r="H18" s="88" t="inlineStr">
         <is>
           <t>Combustible</t>
         </is>
       </c>
       <c r="I18" s="22" t="n"/>
-      <c r="J18" s="32" t="n"/>
-      <c r="K18" s="25" t="n"/>
-      <c r="L18" s="22" t="n"/>
+      <c r="J18" s="102" t="n"/>
+      <c r="K18" s="98" t="n"/>
+      <c r="L18" s="99" t="n"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="27">
       <c r="A19" s="77" t="inlineStr">
@@ -1604,10 +1652,10 @@
       <c r="L20" s="21" t="n"/>
     </row>
     <row r="21" ht="16.95" customHeight="1" s="27">
-      <c r="A21" s="41" t="n">
+      <c r="A21" s="103" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="104" t="inlineStr">
         <is>
           <t>Sin fugas de aceite, combustible ni líquido hidráulico</t>
         </is>
@@ -1618,16 +1666,16 @@
       <c r="F21" s="17" t="n"/>
       <c r="G21" s="17" t="n"/>
       <c r="H21" s="18" t="n"/>
-      <c r="I21" s="41" t="n"/>
-      <c r="J21" s="18" t="n"/>
-      <c r="K21" s="43" t="n"/>
-      <c r="L21" s="18" t="n"/>
+      <c r="I21" s="105" t="n"/>
+      <c r="J21" s="106" t="n"/>
+      <c r="K21" s="107" t="n"/>
+      <c r="L21" s="106" t="n"/>
     </row>
     <row r="22" ht="16.95" customHeight="1" s="27">
-      <c r="A22" s="41" t="n">
+      <c r="A22" s="103" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="104" t="inlineStr">
         <is>
           <t>Mantenimiento preventivo al día (hoja de vida o registro)</t>
         </is>
@@ -1638,16 +1686,16 @@
       <c r="F22" s="17" t="n"/>
       <c r="G22" s="17" t="n"/>
       <c r="H22" s="18" t="n"/>
-      <c r="I22" s="41" t="n"/>
-      <c r="J22" s="18" t="n"/>
-      <c r="K22" s="43" t="n"/>
-      <c r="L22" s="18" t="n"/>
+      <c r="I22" s="105" t="n"/>
+      <c r="J22" s="106" t="n"/>
+      <c r="K22" s="107" t="n"/>
+      <c r="L22" s="106" t="n"/>
     </row>
     <row r="23" ht="16.95" customHeight="1" s="27">
-      <c r="A23" s="41" t="n">
+      <c r="A23" s="103" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="104" t="inlineStr">
         <is>
           <t>Revisión técnico-mecánica y de gases vigente (si aplica)</t>
         </is>
@@ -1658,16 +1706,16 @@
       <c r="F23" s="17" t="n"/>
       <c r="G23" s="17" t="n"/>
       <c r="H23" s="18" t="n"/>
-      <c r="I23" s="41" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="43" t="n"/>
-      <c r="L23" s="18" t="n"/>
+      <c r="I23" s="105" t="n"/>
+      <c r="J23" s="106" t="n"/>
+      <c r="K23" s="107" t="n"/>
+      <c r="L23" s="106" t="n"/>
     </row>
     <row r="24" ht="16.95" customHeight="1" s="27">
-      <c r="A24" s="41" t="n">
+      <c r="A24" s="103" t="n">
         <v>4</v>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="104" t="inlineStr">
         <is>
           <t>Silenciador y encerramientos en buen estado</t>
         </is>
@@ -1678,16 +1726,16 @@
       <c r="F24" s="17" t="n"/>
       <c r="G24" s="17" t="n"/>
       <c r="H24" s="18" t="n"/>
-      <c r="I24" s="41" t="n"/>
-      <c r="J24" s="18" t="n"/>
-      <c r="K24" s="43" t="n"/>
-      <c r="L24" s="18" t="n"/>
+      <c r="I24" s="105" t="n"/>
+      <c r="J24" s="106" t="n"/>
+      <c r="K24" s="107" t="n"/>
+      <c r="L24" s="106" t="n"/>
     </row>
     <row r="25" ht="16.95" customHeight="1" s="27">
-      <c r="A25" s="41" t="n">
+      <c r="A25" s="103" t="n">
         <v>5</v>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="104" t="inlineStr">
         <is>
           <t>Sin humo negro o azul visible al funcionar</t>
         </is>
@@ -1698,16 +1746,16 @@
       <c r="F25" s="17" t="n"/>
       <c r="G25" s="17" t="n"/>
       <c r="H25" s="18" t="n"/>
-      <c r="I25" s="41" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="43" t="n"/>
-      <c r="L25" s="18" t="n"/>
+      <c r="I25" s="105" t="n"/>
+      <c r="J25" s="106" t="n"/>
+      <c r="K25" s="107" t="n"/>
+      <c r="L25" s="106" t="n"/>
     </row>
     <row r="26" ht="16.95" customHeight="1" s="27">
-      <c r="A26" s="41" t="n">
+      <c r="A26" s="103" t="n">
         <v>6</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="104" t="inlineStr">
         <is>
           <t>Kit antiderrames y extintor a bordo o en el sitio</t>
         </is>
@@ -1718,16 +1766,16 @@
       <c r="F26" s="17" t="n"/>
       <c r="G26" s="17" t="n"/>
       <c r="H26" s="18" t="n"/>
-      <c r="I26" s="41" t="n"/>
-      <c r="J26" s="18" t="n"/>
-      <c r="K26" s="43" t="n"/>
-      <c r="L26" s="18" t="n"/>
+      <c r="I26" s="105" t="n"/>
+      <c r="J26" s="106" t="n"/>
+      <c r="K26" s="107" t="n"/>
+      <c r="L26" s="106" t="n"/>
     </row>
     <row r="27" ht="16.95" customHeight="1" s="27">
-      <c r="A27" s="41" t="n">
+      <c r="A27" s="103" t="n">
         <v>7</v>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="104" t="inlineStr">
         <is>
           <t>Bandeja de goteo o piso protegido en el sitio de parqueo</t>
         </is>
@@ -1738,16 +1786,16 @@
       <c r="F27" s="17" t="n"/>
       <c r="G27" s="17" t="n"/>
       <c r="H27" s="18" t="n"/>
-      <c r="I27" s="41" t="n"/>
-      <c r="J27" s="18" t="n"/>
-      <c r="K27" s="43" t="n"/>
-      <c r="L27" s="18" t="n"/>
+      <c r="I27" s="105" t="n"/>
+      <c r="J27" s="106" t="n"/>
+      <c r="K27" s="107" t="n"/>
+      <c r="L27" s="106" t="n"/>
     </row>
     <row r="28" ht="16.95" customHeight="1" s="27">
-      <c r="A28" s="41" t="n">
+      <c r="A28" s="103" t="n">
         <v>8</v>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="104" t="inlineStr">
         <is>
           <t>Equipo limpio, sin lodo ni residuos que se arrastren a la vía</t>
         </is>
@@ -1758,16 +1806,16 @@
       <c r="F28" s="17" t="n"/>
       <c r="G28" s="17" t="n"/>
       <c r="H28" s="18" t="n"/>
-      <c r="I28" s="41" t="n"/>
-      <c r="J28" s="18" t="n"/>
-      <c r="K28" s="43" t="n"/>
-      <c r="L28" s="18" t="n"/>
+      <c r="I28" s="105" t="n"/>
+      <c r="J28" s="106" t="n"/>
+      <c r="K28" s="107" t="n"/>
+      <c r="L28" s="106" t="n"/>
     </row>
     <row r="29" ht="16.95" customHeight="1" s="27">
-      <c r="A29" s="41" t="n">
+      <c r="A29" s="103" t="n">
         <v>9</v>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="104" t="inlineStr">
         <is>
           <t>Residuos del mantenimiento (aceite, filtros, estopas) manejados como residuos peligrosos</t>
         </is>
@@ -1778,16 +1826,16 @@
       <c r="F29" s="17" t="n"/>
       <c r="G29" s="17" t="n"/>
       <c r="H29" s="18" t="n"/>
-      <c r="I29" s="41" t="n"/>
-      <c r="J29" s="18" t="n"/>
-      <c r="K29" s="43" t="n"/>
-      <c r="L29" s="18" t="n"/>
+      <c r="I29" s="105" t="n"/>
+      <c r="J29" s="106" t="n"/>
+      <c r="K29" s="107" t="n"/>
+      <c r="L29" s="106" t="n"/>
     </row>
     <row r="30" ht="16.95" customHeight="1" s="27">
-      <c r="A30" s="41" t="n">
+      <c r="A30" s="103" t="n">
         <v>10</v>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="104" t="inlineStr">
         <is>
           <t>Combustible suministrado con contención y sin derrames</t>
         </is>
@@ -1798,16 +1846,16 @@
       <c r="F30" s="17" t="n"/>
       <c r="G30" s="17" t="n"/>
       <c r="H30" s="18" t="n"/>
-      <c r="I30" s="41" t="n"/>
-      <c r="J30" s="18" t="n"/>
-      <c r="K30" s="43" t="n"/>
-      <c r="L30" s="18" t="n"/>
+      <c r="I30" s="105" t="n"/>
+      <c r="J30" s="106" t="n"/>
+      <c r="K30" s="107" t="n"/>
+      <c r="L30" s="106" t="n"/>
     </row>
     <row r="31" ht="16.95" customHeight="1" s="27">
-      <c r="A31" s="41" t="n">
+      <c r="A31" s="103" t="n">
         <v>11</v>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="104" t="inlineStr">
         <is>
           <t>Alarma de reversa y luces funcionando</t>
         </is>
@@ -1818,16 +1866,16 @@
       <c r="F31" s="17" t="n"/>
       <c r="G31" s="17" t="n"/>
       <c r="H31" s="18" t="n"/>
-      <c r="I31" s="41" t="n"/>
-      <c r="J31" s="18" t="n"/>
-      <c r="K31" s="43" t="n"/>
-      <c r="L31" s="18" t="n"/>
+      <c r="I31" s="105" t="n"/>
+      <c r="J31" s="106" t="n"/>
+      <c r="K31" s="107" t="n"/>
+      <c r="L31" s="106" t="n"/>
     </row>
     <row r="32" ht="16.95" customHeight="1" s="27">
-      <c r="A32" s="41" t="n">
+      <c r="A32" s="103" t="n">
         <v>12</v>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="104" t="inlineStr">
         <is>
           <t>Mangueras y acoples hidráulicos sin fisuras</t>
         </is>
@@ -1838,16 +1886,16 @@
       <c r="F32" s="17" t="n"/>
       <c r="G32" s="17" t="n"/>
       <c r="H32" s="18" t="n"/>
-      <c r="I32" s="41" t="n"/>
-      <c r="J32" s="18" t="n"/>
-      <c r="K32" s="43" t="n"/>
-      <c r="L32" s="18" t="n"/>
+      <c r="I32" s="105" t="n"/>
+      <c r="J32" s="106" t="n"/>
+      <c r="K32" s="107" t="n"/>
+      <c r="L32" s="106" t="n"/>
     </row>
     <row r="33" ht="16.95" customHeight="1" s="27">
-      <c r="A33" s="41" t="n">
+      <c r="A33" s="103" t="n">
         <v>13</v>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="104" t="inlineStr">
         <is>
           <t>Operador capacitado en manejo ambiental y atención de derrames</t>
         </is>
@@ -1858,16 +1906,16 @@
       <c r="F33" s="17" t="n"/>
       <c r="G33" s="17" t="n"/>
       <c r="H33" s="18" t="n"/>
-      <c r="I33" s="41" t="n"/>
-      <c r="J33" s="18" t="n"/>
-      <c r="K33" s="43" t="n"/>
-      <c r="L33" s="18" t="n"/>
+      <c r="I33" s="105" t="n"/>
+      <c r="J33" s="106" t="n"/>
+      <c r="K33" s="107" t="n"/>
+      <c r="L33" s="106" t="n"/>
     </row>
     <row r="34" ht="16.95" customHeight="1" s="27">
-      <c r="A34" s="41" t="n">
+      <c r="A34" s="103" t="n">
         <v>14</v>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="104" t="inlineStr">
         <is>
           <t>Equipo apagado en los tiempos de espera (sin ralentí prolongado)</t>
         </is>
@@ -1878,16 +1926,16 @@
       <c r="F34" s="17" t="n"/>
       <c r="G34" s="17" t="n"/>
       <c r="H34" s="18" t="n"/>
-      <c r="I34" s="41" t="n"/>
-      <c r="J34" s="18" t="n"/>
-      <c r="K34" s="43" t="n"/>
-      <c r="L34" s="18" t="n"/>
+      <c r="I34" s="105" t="n"/>
+      <c r="J34" s="106" t="n"/>
+      <c r="K34" s="107" t="n"/>
+      <c r="L34" s="106" t="n"/>
     </row>
     <row r="35" ht="16.95" customHeight="1" s="27">
-      <c r="A35" s="41" t="n">
+      <c r="A35" s="103" t="n">
         <v>15</v>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="104" t="inlineStr">
         <is>
           <t>Documentos del equipo y del operador al día (SOAT, licencia)</t>
         </is>
@@ -1898,16 +1946,16 @@
       <c r="F35" s="17" t="n"/>
       <c r="G35" s="17" t="n"/>
       <c r="H35" s="18" t="n"/>
-      <c r="I35" s="41" t="n"/>
-      <c r="J35" s="18" t="n"/>
-      <c r="K35" s="43" t="n"/>
-      <c r="L35" s="18" t="n"/>
+      <c r="I35" s="105" t="n"/>
+      <c r="J35" s="106" t="n"/>
+      <c r="K35" s="107" t="n"/>
+      <c r="L35" s="106" t="n"/>
     </row>
     <row r="36" ht="16.95" customHeight="1" s="27">
-      <c r="A36" s="41" t="n">
+      <c r="A36" s="103" t="n">
         <v>16</v>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="104" t="inlineStr">
         <is>
           <t>Registro de consumo de combustible diligenciado</t>
         </is>
@@ -1918,10 +1966,10 @@
       <c r="F36" s="17" t="n"/>
       <c r="G36" s="17" t="n"/>
       <c r="H36" s="18" t="n"/>
-      <c r="I36" s="41" t="n"/>
-      <c r="J36" s="18" t="n"/>
-      <c r="K36" s="43" t="n"/>
-      <c r="L36" s="18" t="n"/>
+      <c r="I36" s="105" t="n"/>
+      <c r="J36" s="106" t="n"/>
+      <c r="K36" s="107" t="n"/>
+      <c r="L36" s="106" t="n"/>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="27">
       <c r="A37" s="77" t="inlineStr">
@@ -1942,7 +1990,7 @@
       <c r="L37" s="18" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="27">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="104" t="inlineStr">
         <is>
           <t>☐ Apto para operar</t>
         </is>
@@ -1950,7 +1998,7 @@
       <c r="B38" s="17" t="n"/>
       <c r="C38" s="17" t="n"/>
       <c r="D38" s="18" t="n"/>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E38" s="104" t="inlineStr">
         <is>
           <t>☐ Apto con observaciones</t>
         </is>
@@ -1958,7 +2006,7 @@
       <c r="F38" s="17" t="n"/>
       <c r="G38" s="17" t="n"/>
       <c r="H38" s="18" t="n"/>
-      <c r="I38" s="16" t="inlineStr">
+      <c r="I38" s="104" t="inlineStr">
         <is>
           <t>☐ No apto: retirar de la operación</t>
         </is>
@@ -1974,16 +2022,16 @@
         </is>
       </c>
       <c r="B39" s="22" t="n"/>
-      <c r="C39" s="23" t="n"/>
-      <c r="D39" s="22" t="n"/>
+      <c r="C39" s="100" t="n"/>
+      <c r="D39" s="99" t="n"/>
       <c r="E39" s="88" t="inlineStr">
         <is>
           <t>Corrección antes del</t>
         </is>
       </c>
       <c r="F39" s="22" t="n"/>
-      <c r="G39" s="23" t="n"/>
-      <c r="H39" s="22" t="n"/>
+      <c r="G39" s="100" t="n"/>
+      <c r="H39" s="99" t="n"/>
     </row>
     <row r="40" ht="16.5" customHeight="1" s="27">
       <c r="A40" s="77" t="inlineStr">
@@ -2004,18 +2052,18 @@
       <c r="L40" s="18" t="n"/>
     </row>
     <row r="41" ht="52.05" customHeight="1" s="27">
-      <c r="A41" s="40" t="n"/>
-      <c r="B41" s="25" t="n"/>
-      <c r="C41" s="25" t="n"/>
-      <c r="D41" s="25" t="n"/>
-      <c r="E41" s="25" t="n"/>
-      <c r="F41" s="25" t="n"/>
-      <c r="G41" s="25" t="n"/>
-      <c r="H41" s="25" t="n"/>
-      <c r="I41" s="25" t="n"/>
-      <c r="J41" s="25" t="n"/>
-      <c r="K41" s="25" t="n"/>
-      <c r="L41" s="22" t="n"/>
+      <c r="A41" s="108" t="n"/>
+      <c r="B41" s="98" t="n"/>
+      <c r="C41" s="98" t="n"/>
+      <c r="D41" s="98" t="n"/>
+      <c r="E41" s="98" t="n"/>
+      <c r="F41" s="98" t="n"/>
+      <c r="G41" s="98" t="n"/>
+      <c r="H41" s="98" t="n"/>
+      <c r="I41" s="98" t="n"/>
+      <c r="J41" s="98" t="n"/>
+      <c r="K41" s="98" t="n"/>
+      <c r="L41" s="99" t="n"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="27">
       <c r="A42" s="77" t="inlineStr">
@@ -2068,24 +2116,24 @@
         </is>
       </c>
       <c r="B44" s="18" t="n"/>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="18" t="n"/>
+      <c r="C44" s="107" t="n"/>
+      <c r="D44" s="106" t="n"/>
       <c r="E44" s="82" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F44" s="18" t="n"/>
-      <c r="G44" s="19" t="n"/>
-      <c r="H44" s="18" t="n"/>
+      <c r="G44" s="107" t="n"/>
+      <c r="H44" s="106" t="n"/>
       <c r="I44" s="82" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="J44" s="18" t="n"/>
-      <c r="K44" s="19" t="n"/>
-      <c r="L44" s="18" t="n"/>
+      <c r="K44" s="107" t="n"/>
+      <c r="L44" s="106" t="n"/>
     </row>
     <row r="45" ht="21" customHeight="1" s="27">
       <c r="A45" s="82" t="inlineStr">
@@ -2094,24 +2142,24 @@
         </is>
       </c>
       <c r="B45" s="18" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="18" t="n"/>
+      <c r="C45" s="107" t="n"/>
+      <c r="D45" s="106" t="n"/>
       <c r="E45" s="82" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="F45" s="18" t="n"/>
-      <c r="G45" s="19" t="n"/>
-      <c r="H45" s="18" t="n"/>
+      <c r="G45" s="107" t="n"/>
+      <c r="H45" s="106" t="n"/>
       <c r="I45" s="82" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="J45" s="18" t="n"/>
-      <c r="K45" s="19" t="n"/>
-      <c r="L45" s="18" t="n"/>
+      <c r="K45" s="107" t="n"/>
+      <c r="L45" s="106" t="n"/>
     </row>
     <row r="46" ht="21" customHeight="1" s="27">
       <c r="A46" s="82" t="inlineStr">
@@ -2120,24 +2168,24 @@
         </is>
       </c>
       <c r="B46" s="18" t="n"/>
-      <c r="C46" s="19" t="n"/>
-      <c r="D46" s="18" t="n"/>
+      <c r="C46" s="107" t="n"/>
+      <c r="D46" s="106" t="n"/>
       <c r="E46" s="82" t="inlineStr">
         <is>
           <t>Cédula:</t>
         </is>
       </c>
       <c r="F46" s="18" t="n"/>
-      <c r="G46" s="19" t="n"/>
-      <c r="H46" s="18" t="n"/>
+      <c r="G46" s="107" t="n"/>
+      <c r="H46" s="106" t="n"/>
       <c r="I46" s="82" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="J46" s="18" t="n"/>
-      <c r="K46" s="19" t="n"/>
-      <c r="L46" s="18" t="n"/>
+      <c r="K46" s="107" t="n"/>
+      <c r="L46" s="106" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -2151,6 +2199,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="127">
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="K24:L24"/>
